--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128377323</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128377323</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,126 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128793751</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bäverhushöjden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>575509</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6970174</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska spår på minst två granar i lämplig biotop för angiven art</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Peter Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>128793751</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128377323</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>128793751</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128377323</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,111 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128999775</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rismyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575506</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6970213</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Norberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Norberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128377323</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128793751</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128999775</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128377323</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128793751</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128999775</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128377323</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>128793751</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128999775</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1011,506 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130058003</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80193</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575401</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6970182</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130057975</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575392</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6970254</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130057974</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575394</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6970263</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130057999</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575387</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6970271</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130058011</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575417</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6970259</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>130058003</v>
       </c>
       <c r="B5" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130057999</v>
+        <v>130058011</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1325,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575387</v>
+        <v>575417</v>
       </c>
       <c r="R8" t="n">
-        <v>6970271</v>
+        <v>6970259</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,11 +1385,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130058011</v>
+        <v>130057999</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,21 +1422,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575417</v>
+        <v>575387</v>
       </c>
       <c r="R9" t="n">
-        <v>6970259</v>
+        <v>6970271</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1482,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130058011</v>
+        <v>130057999</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1325,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575417</v>
+        <v>575387</v>
       </c>
       <c r="R8" t="n">
-        <v>6970259</v>
+        <v>6970271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,6 +1385,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130057999</v>
+        <v>130058011</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,21 +1427,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575387</v>
+        <v>575417</v>
       </c>
       <c r="R9" t="n">
-        <v>6970271</v>
+        <v>6970259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,11 +1487,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>130058003</v>
       </c>
       <c r="B5" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>130057975</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>130057974</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>130057999</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>130058011</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130057999</v>
+        <v>130058011</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1325,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575387</v>
+        <v>575417</v>
       </c>
       <c r="R8" t="n">
-        <v>6970271</v>
+        <v>6970259</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,11 +1385,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130058011</v>
+        <v>130057999</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,21 +1422,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575417</v>
+        <v>575387</v>
       </c>
       <c r="R9" t="n">
-        <v>6970259</v>
+        <v>6970271</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1487,6 +1482,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128377323</v>
+        <v>130058011</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rismyran, Jmt</t>
+          <t>Långmarkflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575394</v>
+        <v>575417</v>
       </c>
       <c r="R2" t="n">
-        <v>6970229</v>
+        <v>6970259</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Norberg</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Norberg</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128793751</v>
+        <v>130058003</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,45 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäverhushöjden, Jmt</t>
+          <t>Långmarkflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575509</v>
+        <v>575401</v>
       </c>
       <c r="R3" t="n">
-        <v>6970174</v>
+        <v>6970182</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,34 +837,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska spår på minst två granar i lämplig biotop för angiven art</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -896,65 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Nilsson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Nilsson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999775</v>
+        <v>130058008</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>80468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rismyran, Jmt</t>
+          <t>Långmarkflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575506</v>
+        <v>575396</v>
       </c>
       <c r="R4" t="n">
-        <v>6970213</v>
+        <v>6970178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Norberg</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Norberg</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130058003</v>
+        <v>128377323</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,37 +977,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmarkflon, Jmt</t>
+          <t>Rismyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575401</v>
+        <v>575394</v>
       </c>
       <c r="R5" t="n">
-        <v>6970182</v>
+        <v>6970229</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,12 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,22 +1067,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Andreas Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Andreas Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130057975</v>
+        <v>128793751</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,19 +1108,27 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmarkflon, Jmt</t>
+          <t>Bäverhushöjden, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575392</v>
+        <v>575509</v>
       </c>
       <c r="R6" t="n">
-        <v>6970254</v>
+        <v>6970174</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,24 +1152,34 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska spår på minst två granar i lämplig biotop för angiven art</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1200,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Peter Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Peter Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130057974</v>
+        <v>128999775</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,17 +1227,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmarkflon, Jmt</t>
+          <t>Rismyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575394</v>
+        <v>575506</v>
       </c>
       <c r="R7" t="n">
-        <v>6970263</v>
+        <v>6970213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,17 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,22 +1292,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Andreas Norberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Andreas Norberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130058011</v>
+        <v>130057974</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1325,21 +1315,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575417</v>
+        <v>575394</v>
       </c>
       <c r="R8" t="n">
-        <v>6970259</v>
+        <v>6970263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,6 +1375,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130057999</v>
+        <v>130057975</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575387</v>
+        <v>575392</v>
       </c>
       <c r="R9" t="n">
-        <v>6970271</v>
+        <v>6970254</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,6 +1505,210 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130057998</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575378</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6970293</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130057999</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575387</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6970271</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33432-2023 artfynd.xlsx
+++ b/artfynd/A 33432-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130058011</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130058003</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130058008</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128377323</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793751</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999775</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057974</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057975</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1607,6 +1652,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057998</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,8 +1759,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130057999</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>